--- a/Xlsx/GlobalString.xlsx
+++ b/Xlsx/GlobalString.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21090" windowHeight="9165"/>
+    <workbookView windowWidth="21090" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Property1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <t>Type</t>
   </si>
   <si>
-    <t>string</t>
+    <t>String</t>
   </si>
   <si>
     <t>Desc</t>

--- a/Xlsx/GlobalString.xlsx
+++ b/Xlsx/GlobalString.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21090" windowHeight="9720"/>
+    <workbookView windowWidth="21570" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="Property1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Value</t>
   </si>
   <si>
-    <t>_Remark</t>
+    <t>#Remark</t>
   </si>
   <si>
     <t>Type</t>
@@ -231,7 +231,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,12 +240,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -431,7 +425,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -446,85 +440,10 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -653,7 +572,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -665,147 +584,126 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1209,40 +1107,37 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:3">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:3">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" s="3" customFormat="1" ht="14.25" spans="1:3">
-      <c r="A3" s="8" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:3">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4">
@@ -1250,7 +1145,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B5">
@@ -1258,7 +1153,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B6">
@@ -1266,58 +1161,58 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="10"/>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="10"/>
+      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="10"/>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="10"/>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="10"/>
+      <c r="A11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="10"/>
+      <c r="A12" s="3"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="10"/>
+      <c r="A13" s="3"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="10"/>
+      <c r="A14" s="3"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="10"/>
+      <c r="A15" s="3"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="10"/>
+      <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="10"/>
+      <c r="A17" s="3"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="10"/>
+      <c r="A18" s="3"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="10"/>
+      <c r="A19" s="3"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="10"/>
+      <c r="A20" s="3"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="10"/>
+      <c r="A21" s="3"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="10"/>
+      <c r="A22" s="3"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="10"/>
+      <c r="A23" s="3"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="10"/>
+      <c r="A24" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
